--- a/MainTop/22.06.2026 Макс ВБ/print_print_sorted.xlsx
+++ b/MainTop/22.06.2026 Макс ВБ/print_print_sorted.xlsx
@@ -5,17 +5,28 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\22.06.2026 Макс ВБ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxim\Documents\GitHub\Ozon_upload\MainTop\22.06.2026 Макс ВБ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB822BE0-33F7-4E0D-AB85-4B6823DF842B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{201B83D2-35F1-4D35-8345-79ABA2AA065F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -34,9 +45,6 @@
     <t>Имя папки</t>
   </si>
   <si>
-    <t>на 4 городов</t>
-  </si>
-  <si>
     <t>Термонаклейка набор Майнкрафт Minecraft в1</t>
   </si>
   <si>
@@ -206,6 +214,9 @@
   </si>
   <si>
     <t>6_а4_настройки_60</t>
+  </si>
+  <si>
+    <t>на 4 города</t>
   </si>
 </sst>
 </file>
@@ -603,12 +614,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="53.5703125" customWidth="1"/>
-    <col min="3" max="3" width="6.140625" customWidth="1"/>
-    <col min="4" max="4" width="19.5703125" customWidth="1"/>
+    <col min="1" max="1" width="48.7109375" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="0.140625" customWidth="1"/>
+    <col min="4" max="4" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -625,21 +637,21 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B2" s="2">
         <v>160</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E2" s="2">
         <v>40</v>
@@ -647,16 +659,16 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" s="2">
         <v>64</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E3" s="2">
         <v>16</v>
@@ -664,16 +676,16 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" s="2">
         <v>48</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E4" s="2">
         <v>12</v>
@@ -681,16 +693,16 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" s="2">
         <v>48</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E5" s="2">
         <v>12</v>
@@ -698,16 +710,16 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6" s="3">
         <v>44</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E6" s="3">
         <v>11</v>
@@ -715,16 +727,16 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" s="3">
         <v>44</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E7" s="3">
         <v>11</v>
@@ -732,16 +744,16 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8" s="3">
         <v>32</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E8" s="3">
         <v>8</v>
@@ -749,16 +761,16 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9" s="3">
         <v>32</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E9" s="3">
         <v>8</v>
@@ -766,16 +778,16 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B10" s="3">
         <v>28</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E10" s="3">
         <v>7</v>
@@ -783,16 +795,16 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B11" s="3">
         <v>24</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E11" s="3">
         <v>6</v>
@@ -800,16 +812,16 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B12" s="3">
         <v>20</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E12" s="3">
         <v>5</v>
@@ -817,16 +829,16 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13" s="3">
         <v>20</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E13" s="3">
         <v>5</v>
@@ -834,16 +846,16 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B14" s="3">
         <v>16</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E14" s="3">
         <v>4</v>
@@ -851,16 +863,16 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B15" s="3">
         <v>12</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E15" s="3">
         <v>3</v>
@@ -868,16 +880,16 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B16" s="3">
         <v>12</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E16" s="3">
         <v>3</v>
@@ -885,16 +897,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B17" s="3">
         <v>8</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E17" s="3">
         <v>2</v>
@@ -902,16 +914,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B18" s="3">
         <v>8</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E18" s="3">
         <v>2</v>
@@ -919,16 +931,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B19" s="3">
         <v>8</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E19" s="3">
         <v>2</v>
@@ -936,16 +948,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B20" s="3">
         <v>8</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E20" s="3">
         <v>2</v>
@@ -953,16 +965,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B21" s="3">
         <v>8</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E21" s="3">
         <v>2</v>
@@ -970,16 +982,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B22" s="3">
         <v>8</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E22" s="3">
         <v>2</v>
@@ -987,16 +999,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B23" s="3">
         <v>4</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E23" s="3">
         <v>1</v>
@@ -1004,16 +1016,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B24" s="3">
         <v>4</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E24" s="3">
         <v>1</v>
@@ -1021,16 +1033,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B25" s="3">
         <v>4</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E25" s="3">
         <v>1</v>
@@ -1038,16 +1050,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B26" s="3">
         <v>4</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E26" s="3">
         <v>1</v>
@@ -1055,16 +1067,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B27" s="4">
         <v>4</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E27" s="4">
         <v>1</v>
@@ -1072,16 +1084,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B28" s="4">
         <v>4</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E28" s="4">
         <v>1</v>
@@ -1089,16 +1101,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B29" s="4">
         <v>4</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E29" s="4">
         <v>1</v>
@@ -1106,16 +1118,16 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B30" s="4">
         <v>64</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E30" s="4">
         <v>16</v>
@@ -1123,16 +1135,16 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B31" s="4">
         <v>32</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E31" s="4">
         <v>8</v>
@@ -1140,16 +1152,16 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B32" s="4">
         <v>28</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E32" s="4">
         <v>7</v>
@@ -1157,16 +1169,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B33" s="4">
         <v>28</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E33" s="4">
         <v>7</v>
@@ -1174,16 +1186,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B34" s="4">
         <v>28</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E34" s="4">
         <v>7</v>
@@ -1191,16 +1203,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B35" s="4">
         <v>16</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E35" s="4">
         <v>4</v>
@@ -1208,16 +1220,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B36" s="4">
         <v>16</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E36" s="4">
         <v>4</v>
@@ -1225,16 +1237,16 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B37" s="4">
         <v>12</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E37" s="4">
         <v>3</v>
@@ -1242,16 +1254,16 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B38" s="4">
         <v>12</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E38" s="4">
         <v>3</v>
@@ -1259,16 +1271,16 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B39" s="4">
         <v>8</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E39" s="4">
         <v>2</v>
@@ -1276,16 +1288,16 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B40" s="4">
         <v>8</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E40" s="4">
         <v>2</v>
@@ -1293,16 +1305,16 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B41" s="4">
         <v>8</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E41" s="4">
         <v>2</v>
@@ -1310,16 +1322,16 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B42" s="4">
         <v>8</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E42" s="4">
         <v>2</v>
@@ -1327,16 +1339,16 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B43" s="4">
         <v>4</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E43" s="4">
         <v>1</v>
@@ -1344,16 +1356,16 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B44" s="4">
         <v>4</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E44" s="4">
         <v>1</v>
@@ -1361,16 +1373,16 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B45" s="4">
         <v>4</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E45" s="4">
         <v>1</v>
@@ -1378,16 +1390,16 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B46" s="4">
         <v>4</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E46" s="4">
         <v>1</v>
@@ -1395,16 +1407,16 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B47" s="4">
         <v>4</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E47" s="4">
         <v>1</v>
@@ -1412,16 +1424,16 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B48" s="4">
         <v>4</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E48" s="4">
         <v>1</v>
@@ -1429,16 +1441,16 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B49" s="4">
         <v>4</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E49" s="4">
         <v>1</v>
@@ -1446,16 +1458,16 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B50" s="4">
         <v>4</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E50" s="4">
         <v>1</v>
@@ -1463,16 +1475,16 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B51" s="5">
         <v>72</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E51" s="5">
         <v>18</v>
@@ -1480,16 +1492,16 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B52" s="5">
         <v>4</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E52" s="5">
         <v>1</v>
@@ -1497,22 +1509,29 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B53" s="6">
         <v>60</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E53" s="6">
         <v>15</v>
       </c>
     </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E54">
+        <f>SUM(E2:E53)</f>
+        <v>279</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>